--- a/data/trans_bre/IP26C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 8,08</t>
+          <t>-3,57; 8,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 5,96</t>
+          <t>-6,61; 5,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,88</t>
+          <t>-7,18; 3,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 5,64</t>
+          <t>-9,61; 6,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 120,49</t>
+          <t>-30,76; 124,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 71,23</t>
+          <t>-48,12; 68,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-68,17; 54,99</t>
+          <t>-69,07; 56,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 58,69</t>
+          <t>-51,04; 64,5</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 8,93</t>
+          <t>-0,95; 8,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 0,91</t>
+          <t>-8,39; 0,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 4,12</t>
+          <t>-4,61; 3,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 4,03</t>
+          <t>-6,76; 4,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 111,6</t>
+          <t>-9,01; 109,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,78; 13,42</t>
+          <t>-57,79; 9,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 65,16</t>
+          <t>-42,73; 61,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,99; 38,82</t>
+          <t>-42,84; 45,05</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 3,22</t>
+          <t>-7,34; 3,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 3,74</t>
+          <t>-6,4; 4,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 7,43</t>
+          <t>-4,18; 7,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 4,31</t>
+          <t>-4,39; 4,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 45,5</t>
+          <t>-53,95; 49,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 57,03</t>
+          <t>-53,91; 67,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 98,02</t>
+          <t>-33,35; 94,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,62; 116,93</t>
+          <t>-54,86; 111,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 8,62</t>
+          <t>-1,3; 8,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 8,95</t>
+          <t>-2,58; 8,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 5,7</t>
+          <t>-4,31; 5,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 1,13</t>
+          <t>-9,15; 1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 149,48</t>
+          <t>-14,02; 145,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 105,9</t>
+          <t>-20,51; 112,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 75,68</t>
+          <t>-34,42; 79,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 17,36</t>
+          <t>-65,16; 15,81</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,05</t>
+          <t>-0,54; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,11</t>
+          <t>-3,31; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,38</t>
+          <t>-2,4; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,84</t>
+          <t>-4,7; 0,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 59,8</t>
+          <t>-4,87; 56,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 22,23</t>
+          <t>-27,02; 22,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 29,0</t>
+          <t>-23,71; 31,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 8,52</t>
+          <t>-38,63; 8,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 8,23</t>
+          <t>-3,64; 7,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 5,59</t>
+          <t>-5,79; 6,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 3,21</t>
+          <t>-7,26; 3,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 6,06</t>
+          <t>-8,97; 5,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 124,18</t>
+          <t>-31,19; 112,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 68,51</t>
+          <t>-42,12; 78,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-69,07; 56,19</t>
+          <t>-68,9; 65,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 64,5</t>
+          <t>-49,86; 63,37</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 8,95</t>
+          <t>-0,82; 8,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 0,68</t>
+          <t>-8,05; 0,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 3,77</t>
+          <t>-4,44; 4,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 4,51</t>
+          <t>-6,73; 3,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 109,78</t>
+          <t>-6,87; 115,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,79; 9,77</t>
+          <t>-57,26; 12,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 61,0</t>
+          <t>-42,86; 69,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 45,05</t>
+          <t>-42,77; 37,79</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 3,28</t>
+          <t>-7,4; 3,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 4,0</t>
+          <t>-6,24; 3,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 7,53</t>
+          <t>-3,53; 7,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,7</t>
+          <t>-5,11; 4,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,95; 49,06</t>
+          <t>-56,8; 50,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 67,17</t>
+          <t>-54,51; 54,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,35; 94,67</t>
+          <t>-28,63; 98,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 111,85</t>
+          <t>-54,82; 124,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 8,45</t>
+          <t>-1,25; 8,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 8,89</t>
+          <t>-2,72; 8,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 5,82</t>
+          <t>-4,89; 5,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 1,1</t>
+          <t>-9,21; 1,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 145,01</t>
+          <t>-14,9; 143,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 112,77</t>
+          <t>-20,6; 106,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 79,61</t>
+          <t>-38,33; 73,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,16; 15,81</t>
+          <t>-63,98; 22,5</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,62</t>
+          <t>-0,57; 4,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,04</t>
+          <t>-3,2; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,56</t>
+          <t>-2,4; 2,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,82</t>
+          <t>-4,9; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 56,73</t>
+          <t>-5,53; 56,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 22,26</t>
+          <t>-26,11; 21,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 31,76</t>
+          <t>-23,06; 35,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 8,11</t>
+          <t>-39,27; 9,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-10,19%</t>
+          <t>-22,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 7,96</t>
+          <t>-2,95; 8,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 6,28</t>
+          <t>-7,11; 5,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 3,11</t>
+          <t>-7,17; 2,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 5,83</t>
+          <t>-11,83; 3,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 112,52</t>
+          <t>-26,51; 120,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 78,97</t>
+          <t>-49,57; 71,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-68,9; 65,7</t>
+          <t>-68,17; 54,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 63,37</t>
+          <t>-56,69; 37,43</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,95%</t>
+          <t>-4,51%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 8,95</t>
+          <t>-1,01; 8,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 0,96</t>
+          <t>-8,55; 0,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 4,06</t>
+          <t>-4,8; 4,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 3,88</t>
+          <t>-6,68; 4,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 115,13</t>
+          <t>-9,02; 111,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 12,13</t>
+          <t>-58,78; 13,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 69,76</t>
+          <t>-45,16; 65,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,77; 37,79</t>
+          <t>-42,49; 48,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 3,73</t>
+          <t>-7,54; 3,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 3,6</t>
+          <t>-6,79; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 7,67</t>
+          <t>-3,91; 7,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 4,7</t>
+          <t>-4,18; 5,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 50,62</t>
+          <t>-54,2; 45,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 54,73</t>
+          <t>-55,45; 57,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 98,28</t>
+          <t>-32,16; 98,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 124,39</t>
+          <t>-46,13; 149,62</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,99</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-35,66%</t>
+          <t>-32,96%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 8,22</t>
+          <t>-1,12; 8,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 8,67</t>
+          <t>-2,68; 8,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,51</t>
+          <t>-4,2; 5,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 1,3</t>
+          <t>-9,22; 1,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 143,66</t>
+          <t>-13,7; 149,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 106,07</t>
+          <t>-20,15; 105,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 73,02</t>
+          <t>-35,91; 75,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 22,5</t>
+          <t>-64,7; 20,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-17,29%</t>
+          <t>-14,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,71</t>
+          <t>-0,24; 5,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,0</t>
+          <t>-2,94; 2,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,81</t>
+          <t>-2,42; 2,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,88</t>
+          <t>-4,57; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 56,3</t>
+          <t>-2,57; 59,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 21,34</t>
+          <t>-24,57; 22,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 35,39</t>
+          <t>-23,05; 29,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 9,51</t>
+          <t>-34,55; 11,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-3,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-27,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-22,02%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.390542930329287</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.4351007457325126</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.245250596303913</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.319620431794386</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.252597733165311</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.03807965067154397</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.2727056153458933</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2202467775282312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,95; 8,08</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,11; 5,96</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 2,88</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,83; 3,81</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-26,51; 120,49</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-49,57; 71,23</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-68,17; 54,99</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-56,69; 37,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.954522341495284</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.106974372958712</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.167137705739393</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.82729808696873</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2650916625698226</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4957445295559325</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6817288945002885</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5669499538196348</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.075912461760511</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.956083760742873</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.876463249465842</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.807117702391456</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.204898158564967</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.7122552724372082</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.5499049786204474</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.3743028372132799</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>39,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-31,1%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-3,16%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-4,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,01; 8,93</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-8,55; 0,91</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,8; 4,12</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-6,68; 4,77</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-9,02; 111,6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-58,78; 13,42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-45,16; 65,16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-42,49; 48,14</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.977153809138623</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3.707336854085921</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2711814255455414</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.5774528442210367</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3905558916874344</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3110169396269878</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.03164512207229719</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.04508427025478506</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-20,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-15,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16,32%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.008536339238703</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-8.549636586740114</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.800822818758266</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-6.679135638272863</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.09020686127767895</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5877849650484421</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.451595743607955</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4248731817511559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,54; 3,22</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,79; 3,74</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,91; 7,43</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,18; 5,63</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-54,2; 45,5</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-55,45; 57,03</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-32,16; 98,02</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-46,13; 149,62</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.933188927233358</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9114060449953707</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.118514224119528</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.768434372229421</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.115995306451936</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1342366025381092</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6515893417298741</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.481431707600668</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,35</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,75</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-32,96%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.176037959053605</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.446890101537607</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.704471727474055</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.017557114459115</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2041162652932546</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1565399844120254</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.1681434423047172</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1632179014134846</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,12; 8,62</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,68; 8,95</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,2; 5,7</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-9,22; 1,38</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-13,7; 149,48</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-20,15; 105,9</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-35,91; 75,68</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-64,7; 20,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.543785631604498</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.788068005028721</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.913810388775751</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.176077357190744</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5419906590841526</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5544842552956278</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3216290190385645</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4613378906015823</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.222031449381074</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.735157493139458</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.429729684508763</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.63172645140498</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.4550311041342541</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.570261934670523</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.980176826787147</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.496151958141892</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3.399934128362406</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.353649708003356</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6855829286401285</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.752931485654994</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4376038076189382</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3114447754969452</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.06732906383843373</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3296299703373572</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.117994950408534</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.678652078427911</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.195358754220138</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-9.221751495685551</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1369723415238082</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2014757690783156</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3590939551204198</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6469662146498257</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.621619206548303</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.954691955664314</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.699303541485254</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.381790159883979</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.494803573506944</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.058992455166482</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7567999920830085</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2084144034768995</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-4,62%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-14,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,24; 5,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,94; 2,11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 2,38</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,57; 1,06</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 59,8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-24,57; 22,23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-23,05; 29,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-34,55; 11,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.18668960023648</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5043199453750785</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1082508893619716</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.610942901591542</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.231788628049038</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.04622175169089576</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.01164537794615412</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1426292529669791</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.2363277152559292</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.9361848507163</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.422760957011231</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.566567269393126</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.0256771119128923</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2457016873010037</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2304963226366993</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3455460429331322</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.048634675393853</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.111667331910583</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.376382194216286</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.057913882672275</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5979666051858641</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2222727458325775</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2899793846663513</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1125027260278271</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
